--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-14.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-14.xlsx
@@ -474,622 +474,622 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583991840848</v>
+        <v>5583988626779</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Celio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Larissa Padilha Dantas</t>
+          <t>Celio Roberto Tavares Santos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583987335622</v>
+        <v>5583988019693</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jose Joel de Souza</t>
+          <t>Renata Rodrigues da Silva</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583999889560</v>
+        <v>5551997787396</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anselmo</t>
+          <t>Cezar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anselmo de Albuquerque Lisboa Junior</t>
+          <t>Cezar Lopes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583996752927</v>
+        <v>5511994391967</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Valmir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa de Apoio Santa Paulina</t>
+          <t>Valmir Santos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583999918146</v>
+        <v>5583993817338</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Severina</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Severina Paulino Araujo</t>
+          <t>Jose Dionisio da Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988635207</v>
+        <v>5511952886611</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Antonio Felisminino do Nascimento</t>
+          <t>Renata Silva Branco de Andrade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583993420178</v>
+        <v>5583987096594</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Arnaldo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>W F</t>
+          <t>Arnaldo Pereira Alves</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583999011750</v>
+        <v>5583996300462</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celio</t>
+          <t>Vanicleide</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Celio Urquiza</t>
+          <t>Vanicleide Deodato dos Santos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987617660</v>
+        <v>5583991840848</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ana Eloiza Nascimento da Silva</t>
+          <t>Larissa Padilha Dantas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583987146900</v>
+        <v>5583987335622</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Residencial Maria das Dores</t>
+          <t>Jose Joel de Souza</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987453273</v>
+        <v>5583999889560</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jhonatan</t>
+          <t>Anselmo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jhonatan Clementino Ramos</t>
+          <t>Anselmo de Albuquerque Lisboa Junior</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583998467767</v>
+        <v>5583996752927</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Construtora</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Construtora Marsol</t>
+          <t>Casa de Apoio Santa Paulina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583999118230</v>
+        <v>5583999918146</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rafaella</t>
+          <t>Severina</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rafaella Constantino de Freitas</t>
+          <t>Severina Paulino Araujo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583996369667</v>
+        <v>5583988635207</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rodolfo</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rodolfo do Nascimento Castelo Branco</t>
+          <t>Antonio Felisminino do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583998567410</v>
+        <v>5583993420178</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jose Martins dos Santos Filho</t>
+          <t>W F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988423162</v>
+        <v>5583999011750</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Celio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marcia Simplicio da Silva</t>
+          <t>Celio Urquiza</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5511975642844</v>
+        <v>5583987617660</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Carvalho</t>
+          <t>Ana Eloiza Nascimento da Silva</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583982023155</v>
+        <v>5583987146900</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fabricio</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fabricio Gomes Alves</t>
+          <t>Residencial Maria das Dores</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583986840219</v>
+        <v>5583987453273</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Jhonatan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rodrigo Cristiano Alcantara de Castro</t>
+          <t>Jhonatan Clementino Ramos</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988204844</v>
+        <v>5583998467767</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Construtora</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mario Lucas dos Santos Ferreira</t>
+          <t>Construtora Marsol</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583991139628</v>
+        <v>5583999118230</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Rafaella</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Artur Ramos de Andrade Silva</t>
+          <t>Rafaella Constantino de Freitas</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583996041631</v>
+        <v>5583996369667</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marilene</t>
+          <t>Rodolfo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marilene Martins Lima dos Santos</t>
+          <t>Rodolfo do Nascimento Castelo Branco</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5581981770402</v>
+        <v>5583998567410</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maria de Fatima de Lira Soares</t>
+          <t>Jose Martins dos Santos Filho</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583996773190</v>
+        <v>5583988423162</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paulo de Tarso da Silva</t>
+          <t>Marcia Simplicio da Silva</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583988889427</v>
+        <v>5511975642844</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Francisco das Chagas da Silva</t>
+          <t>David Carvalho</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987088300</v>
+        <v>5583982023155</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sandro</t>
+          <t>Fabricio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sandro Andre Felix de Lima</t>
+          <t>Fabricio Gomes Alves</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583987794132</v>
+        <v>5583986840219</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wesley Bruno Souza Lucena</t>
+          <t>Rodrigo Cristiano Alcantara de Castro</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5592982849626</v>
+        <v>5583988204844</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jose Alves Junior</t>
+          <t>Mario Lucas dos Santos Ferreira</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583986340033</v>
+        <v>5583991139628</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zilda</t>
+          <t>Artur</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zilda de Souza Santos</t>
+          <t>Artur Ramos de Andrade Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583996066989</v>
+        <v>5583996041631</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Marilene</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elaine Cristina Camelo de Souza</t>
+          <t>Marilene Martins Lima dos Santos</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988956121</v>
+        <v>5581981770402</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eduardo Felix Amaral</t>
+          <t>Maria de Fatima de Lira Soares</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583993880916</v>
+        <v>5583996773190</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Romildo</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romildo Alves de Brito</t>
+          <t>Paulo de Tarso da Silva</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583988942785</v>
+        <v>5583988889427</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Maria Gicelia Lopes de Souza</t>
+          <t>Francisco das Chagas da Silva</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583999060199</v>
+        <v>5583987088300</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Sandro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jose Laurentino Silva de Farias Junior</t>
+          <t>Sandro Andre Felix de Lima</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986098616</v>
+        <v>5583987794132</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ayanne</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ayanne Mikaelle Limeira de Sousa</t>
+          <t>Wesley Bruno Souza Lucena</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583986634575</v>
+        <v>5592982849626</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Helianar</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Helianar Maria de Assis Meireles</t>
+          <t>Jose Alves Junior</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5511994279985</v>
+        <v>5583986340033</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Zilda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Carlos Eduardo dos Santos Souza</t>
+          <t>Zilda de Souza Santos</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583999802326</v>
+        <v>5583996066989</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marinalva</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Marinalva de Araujo Silva</t>
+          <t>Elaine Cristina Camelo de Souza</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583993011959</v>
+        <v>5583988956121</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maria Vitoria Borges</t>
+          <t>Eduardo Felix Amaral</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5596981029283</v>
+        <v>5583993880916</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Romildo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Andrew Oliveira</t>
+          <t>Romildo Alves de Brito</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583991885783</v>
+        <v>5583988942785</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ezildo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ezildo Felix de Lima</t>
+          <t>Maria Gicelia Lopes de Souza</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583988548089</v>
+        <v>5583999060199</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1098,127 +1098,127 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jose Januncio Verissimo da Silva</t>
+          <t>Jose Laurentino Silva de Farias Junior</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583996181993</v>
+        <v>5583986098616</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lucia</t>
+          <t>Ayanne</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lucia Medeiros</t>
+          <t>Ayanne Mikaelle Limeira de Sousa</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583998114186</v>
+        <v>5583986634575</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rayan</t>
+          <t>Helianar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rayan Honorio da Silva</t>
+          <t>Helianar Maria de Assis Meireles</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583981597656</v>
+        <v>5511994279985</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thiberio</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thiberio Rickelly Pereira de Matos</t>
+          <t>Carlos Eduardo dos Santos Souza</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583996942142</v>
+        <v>5583999802326</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Elcio</t>
+          <t>Marinalva</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Elcio Dias Meira</t>
+          <t>Marinalva de Araujo Silva</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583988502451</v>
+        <v>5583993011959</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Americo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Americo da Silva</t>
+          <t>Maria Vitoria Borges</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583986345900</v>
+        <v>5596981029283</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amaralina</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Amaralina de Assis Meireles</t>
+          <t>Andrew Oliveira</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583998948060</v>
+        <v>5583991885783</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Giovanna</t>
+          <t>Ezildo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Giovanna Karen Silva de Carvalho</t>
+          <t>Ezildo Felix de Lima</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583999220728</v>
+        <v>5583988548089</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Robson Fernandes da Silva</t>
+          <t>Jose Januncio Verissimo da Silva</t>
         </is>
       </c>
     </row>
